--- a/outputs/rankings/top20_ranking.xlsx
+++ b/outputs/rankings/top20_ranking.xlsx
@@ -546,10 +546,10 @@
         <v>2856</v>
       </c>
       <c r="H2" t="n">
-        <v>90.46927710843374</v>
+        <v>91.68915662650603</v>
       </c>
       <c r="I2" t="n">
-        <v>84.59839357429718</v>
+        <v>87.30923694779116</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -582,11 +582,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Florian Wirtz</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -595,34 +595,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2351</v>
+        <v>2041</v>
       </c>
       <c r="H3" t="n">
-        <v>87.70384615384616</v>
+        <v>88.66153846153847</v>
       </c>
       <c r="I3" t="n">
-        <v>87.56410256410258</v>
+        <v>87.69230769230771</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="Q3" t="n">
         <v>177</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sávio</t>
+          <t>Bradley Barcola</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -656,34 +656,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1766</v>
+        <v>2181</v>
       </c>
       <c r="H4" t="n">
-        <v>86.82474182444062</v>
+        <v>87.69698795180723</v>
       </c>
       <c r="I4" t="n">
-        <v>84.61847389558233</v>
+        <v>87.77108433734941</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>66.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="L4" t="n">
-        <v>91.64285714285714</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>200000</v>
+        <v>70000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
@@ -704,11 +704,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rayan Cherki</t>
+          <t>Florian Wirtz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -717,34 +717,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2041</v>
+        <v>2351</v>
       </c>
       <c r="H5" t="n">
-        <v>86.46923076923078</v>
+        <v>87.35769230769232</v>
       </c>
       <c r="I5" t="n">
-        <v>82.82051282051283</v>
+        <v>86.79487179487181</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>66.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>90000000</v>
+        <v>100000000</v>
       </c>
       <c r="Q5" t="n">
         <v>177</v>
@@ -790,10 +790,10 @@
         <v>1730</v>
       </c>
       <c r="H6" t="n">
-        <v>85.98248709122204</v>
+        <v>86.93128227194494</v>
       </c>
       <c r="I6" t="n">
-        <v>82.73092369477914</v>
+        <v>84.8393574297189</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
@@ -826,11 +826,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bradley Barcola</t>
+          <t>Sávio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -839,34 +839,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2181</v>
+        <v>1766</v>
       </c>
       <c r="H7" t="n">
-        <v>85.82650602409639</v>
+        <v>85.48739242685025</v>
       </c>
       <c r="I7" t="n">
-        <v>83.6144578313253</v>
+        <v>81.64658634538152</v>
       </c>
       <c r="J7" t="n">
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>91.64285714285714</v>
       </c>
       <c r="M7" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -875,10 +875,10 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>70000000</v>
+        <v>200000</v>
       </c>
       <c r="Q7" t="n">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -887,7 +887,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>João Neves</t>
+          <t>Nicolás Paz</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -895,27 +895,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1844</v>
+        <v>2687</v>
       </c>
       <c r="H8" t="n">
-        <v>84.29285714285716</v>
+        <v>84.10481927710845</v>
       </c>
       <c r="I8" t="n">
-        <v>77.61904761904762</v>
+        <v>74.89959839357429</v>
       </c>
       <c r="J8" t="n">
         <v>100</v>
@@ -924,10 +924,10 @@
         <v>73.33333333333334</v>
       </c>
       <c r="L8" t="n">
-        <v>94.42857142857143</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>140000000</v>
+        <v>400000</v>
       </c>
       <c r="Q8" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -948,47 +948,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Matìas Soulé</t>
+          <t>João Neves</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1781</v>
+        <v>1844</v>
       </c>
       <c r="H9" t="n">
-        <v>83.0731712564544</v>
+        <v>83.82142857142857</v>
       </c>
       <c r="I9" t="n">
-        <v>79.65863453815261</v>
+        <v>76.57142857142857</v>
       </c>
       <c r="J9" t="n">
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="L9" t="n">
-        <v>92.17857142857142</v>
+        <v>94.42857142857143</v>
       </c>
       <c r="M9" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>35000000</v>
+        <v>140000000</v>
       </c>
       <c r="Q9" t="n">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nicolás Paz</t>
+          <t>Alejandro Garnacho</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1022,34 +1022,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2687</v>
+        <v>2199</v>
       </c>
       <c r="H10" t="n">
-        <v>82.86686746987952</v>
+        <v>83.65963855421687</v>
       </c>
       <c r="I10" t="n">
-        <v>72.14859437751004</v>
+        <v>74.7991967871486</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="L10" t="n">
         <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>400000</v>
+        <v>28000000</v>
       </c>
       <c r="Q10" t="n">
         <v>180</v>
@@ -1070,20 +1070,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamie Gittens</t>
+          <t>Xavi Simons</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1092,22 +1092,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1776</v>
+        <v>2150</v>
       </c>
       <c r="H11" t="n">
-        <v>82.7777108433735</v>
+        <v>83.34807692307693</v>
       </c>
       <c r="I11" t="n">
-        <v>74.83935742971887</v>
+        <v>77.8846153846154</v>
       </c>
       <c r="J11" t="n">
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>73.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
         <v>93</v>
@@ -1119,10 +1119,10 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>30000000</v>
+        <v>40000000</v>
       </c>
       <c r="Q11" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1131,47 +1131,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho</t>
+          <t>Arda Güler</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2199</v>
+        <v>1250</v>
       </c>
       <c r="H12" t="n">
-        <v>82.51204819277109</v>
+        <v>83.33406593406595</v>
       </c>
       <c r="I12" t="n">
-        <v>72.24899598393574</v>
+        <v>82.11538461538463</v>
       </c>
       <c r="J12" t="n">
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>73.21428571428572</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>28000000</v>
+        <v>90000000</v>
       </c>
       <c r="Q12" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1217,10 +1217,10 @@
         <v>1750</v>
       </c>
       <c r="H13" t="n">
-        <v>82.0775817555938</v>
+        <v>83.11673838209983</v>
       </c>
       <c r="I13" t="n">
-        <v>73.81526104417669</v>
+        <v>76.12449799196786</v>
       </c>
       <c r="J13" t="n">
         <v>100</v>
@@ -1253,47 +1253,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Jamie Gittens</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2879</v>
+        <v>1776</v>
       </c>
       <c r="H14" t="n">
-        <v>81.61428571428573</v>
+        <v>83.09397590361446</v>
       </c>
       <c r="I14" t="n">
-        <v>73.80952380952381</v>
+        <v>75.5421686746988</v>
       </c>
       <c r="J14" t="n">
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>60</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="L14" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M14" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1302,10 +1302,10 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>150000000</v>
+        <v>30000000</v>
       </c>
       <c r="Q14" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xavi Simons</t>
+          <t>Jamal Musiala</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2150</v>
+        <v>1798</v>
       </c>
       <c r="H15" t="n">
-        <v>81.50192307692309</v>
+        <v>82.35247252747253</v>
       </c>
       <c r="I15" t="n">
-        <v>73.7820512820513</v>
+        <v>78.07692307692309</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>
@@ -1351,7 +1351,7 @@
         <v>60</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>92.78571428571428</v>
       </c>
       <c r="M15" t="n">
         <v>93</v>
@@ -1363,10 +1363,10 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="Q15" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tom Bischof</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1388,34 +1388,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2559</v>
+        <v>2879</v>
       </c>
       <c r="H16" t="n">
-        <v>81.39285714285714</v>
+        <v>81.67857142857143</v>
       </c>
       <c r="I16" t="n">
-        <v>69.0952380952381</v>
+        <v>73.95238095238095</v>
       </c>
       <c r="J16" t="n">
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>73.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="L16" t="n">
         <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>40000000</v>
+        <v>150000000</v>
       </c>
       <c r="Q16" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arda Güler</t>
+          <t>Tom Bischof</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1444,27 +1444,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1250</v>
+        <v>2559</v>
       </c>
       <c r="H17" t="n">
-        <v>81.19945054945057</v>
+        <v>81.56428571428572</v>
       </c>
       <c r="I17" t="n">
-        <v>77.37179487179489</v>
+        <v>69.47619047619048</v>
       </c>
       <c r="J17" t="n">
         <v>100</v>
@@ -1473,10 +1473,10 @@
         <v>73.33333333333334</v>
       </c>
       <c r="L17" t="n">
-        <v>73.21428571428572</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1485,10 +1485,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>90000000</v>
+        <v>40000000</v>
       </c>
       <c r="Q17" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
@@ -1497,47 +1497,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Warren Zaïre-Emery</t>
+          <t>Yankuba Minteh</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2050</v>
+        <v>1838</v>
       </c>
       <c r="H18" t="n">
-        <v>81.07142857142858</v>
+        <v>81.54479345955249</v>
       </c>
       <c r="I18" t="n">
-        <v>66.38095238095239</v>
+        <v>72.0281124497992</v>
       </c>
       <c r="J18" t="n">
         <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>80</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>94.21428571428571</v>
       </c>
       <c r="M18" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1546,10 +1546,10 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>80000000</v>
+        <v>45000000</v>
       </c>
       <c r="Q18" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yankuba Minteh</t>
+          <t>Warren Zaïre-Emery</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1838</v>
+        <v>2050</v>
       </c>
       <c r="H19" t="n">
-        <v>80.9393717728055</v>
+        <v>81.2</v>
       </c>
       <c r="I19" t="n">
-        <v>70.68273092369478</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="J19" t="n">
         <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>66.66666666666666</v>
+        <v>80</v>
       </c>
       <c r="L19" t="n">
-        <v>94.21428571428571</v>
+        <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1607,10 +1607,10 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>45000000</v>
+        <v>80000000</v>
       </c>
       <c r="Q19" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jamal Musiala</t>
+          <t>Matìas Soulé</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1798</v>
+        <v>1781</v>
       </c>
       <c r="H20" t="n">
-        <v>80.73708791208792</v>
+        <v>80.90449655765921</v>
       </c>
       <c r="I20" t="n">
-        <v>74.4871794871795</v>
+        <v>74.83935742971887</v>
       </c>
       <c r="J20" t="n">
         <v>100</v>
@@ -1656,10 +1656,10 @@
         <v>60</v>
       </c>
       <c r="L20" t="n">
-        <v>92.78571428571428</v>
+        <v>92.17857142857142</v>
       </c>
       <c r="M20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>100000000</v>
+        <v>35000000</v>
       </c>
       <c r="Q20" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21">
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mohamed Ali Cho</t>
+          <t>Kenan Yıldız</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1693,46 +1693,46 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1621</v>
+        <v>2402</v>
       </c>
       <c r="H21" t="n">
-        <v>80.16060671256456</v>
+        <v>80.10180722891567</v>
       </c>
       <c r="I21" t="n">
-        <v>73.31325301204819</v>
+        <v>72.6706827309237</v>
       </c>
       <c r="J21" t="n">
         <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="L21" t="n">
-        <v>86.46428571428572</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>15000000</v>
+        <v>75000000</v>
       </c>
       <c r="Q21" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
